--- a/datafile/df_tsa.xlsx
+++ b/datafile/df_tsa.xlsx
@@ -622,7 +622,7 @@
         <v>2608430</v>
       </c>
       <c r="C17" t="n">
-        <v>34646</v>
+        <v>34645</v>
       </c>
     </row>
     <row r="18">
@@ -644,7 +644,7 @@
         <v>2231469</v>
       </c>
       <c r="C19" t="n">
-        <v>35387</v>
+        <v>35386</v>
       </c>
     </row>
     <row r="20">
@@ -699,7 +699,7 @@
         <v>2243481</v>
       </c>
       <c r="C24" t="n">
-        <v>30627</v>
+        <v>30625</v>
       </c>
     </row>
     <row r="25">
@@ -732,7 +732,7 @@
         <v>1830079</v>
       </c>
       <c r="C27" t="n">
-        <v>27147</v>
+        <v>27145</v>
       </c>
     </row>
     <row r="28">
@@ -1095,7 +1095,7 @@
         <v>2190541</v>
       </c>
       <c r="C60" t="n">
-        <v>30587</v>
+        <v>30586</v>
       </c>
     </row>
     <row r="61">
@@ -1392,7 +1392,7 @@
         <v>2744893</v>
       </c>
       <c r="C87" t="n">
-        <v>39185</v>
+        <v>39184</v>
       </c>
     </row>
     <row r="88">
@@ -1425,7 +1425,7 @@
         <v>2533621</v>
       </c>
       <c r="C90" t="n">
-        <v>38741</v>
+        <v>38740</v>
       </c>
     </row>
     <row r="91">
@@ -1909,7 +1909,7 @@
         <v>2399389</v>
       </c>
       <c r="C134" t="n">
-        <v>33060</v>
+        <v>33059</v>
       </c>
     </row>
     <row r="135">
@@ -1942,7 +1942,7 @@
         <v>2260950</v>
       </c>
       <c r="C137" t="n">
-        <v>36626</v>
+        <v>36624</v>
       </c>
     </row>
     <row r="138">
@@ -1964,7 +1964,7 @@
         <v>2782578</v>
       </c>
       <c r="C139" t="n">
-        <v>41132</v>
+        <v>41131</v>
       </c>
     </row>
     <row r="140">
@@ -1975,7 +1975,7 @@
         <v>2313392</v>
       </c>
       <c r="C140" t="n">
-        <v>34373</v>
+        <v>34372</v>
       </c>
     </row>
     <row r="141">
@@ -2008,7 +2008,7 @@
         <v>2976209</v>
       </c>
       <c r="C143" t="n">
-        <v>48788</v>
+        <v>48790</v>
       </c>
     </row>
     <row r="144">
@@ -2019,7 +2019,7 @@
         <v>2380377</v>
       </c>
       <c r="C144" t="n">
-        <v>40398</v>
+        <v>40397</v>
       </c>
     </row>
     <row r="145">
@@ -2063,7 +2063,7 @@
         <v>2374930</v>
       </c>
       <c r="C148" t="n">
-        <v>38365</v>
+        <v>38364</v>
       </c>
     </row>
     <row r="149">
@@ -2195,7 +2195,7 @@
         <v>2764691</v>
       </c>
       <c r="C160" t="n">
-        <v>41657</v>
+        <v>41656</v>
       </c>
     </row>
     <row r="161">
@@ -2206,7 +2206,7 @@
         <v>2360445</v>
       </c>
       <c r="C161" t="n">
-        <v>35618</v>
+        <v>35617</v>
       </c>
     </row>
     <row r="162">
@@ -2217,7 +2217,7 @@
         <v>2517148</v>
       </c>
       <c r="C162" t="n">
-        <v>36455</v>
+        <v>36450</v>
       </c>
     </row>
     <row r="163">
@@ -2239,7 +2239,7 @@
         <v>2873210</v>
       </c>
       <c r="C164" t="n">
-        <v>44884</v>
+        <v>44883</v>
       </c>
     </row>
     <row r="165">
@@ -2250,7 +2250,7 @@
         <v>2534457</v>
       </c>
       <c r="C165" t="n">
-        <v>39365</v>
+        <v>39361</v>
       </c>
     </row>
     <row r="166">
@@ -2261,7 +2261,7 @@
         <v>2891326</v>
       </c>
       <c r="C166" t="n">
-        <v>44652</v>
+        <v>44649</v>
       </c>
     </row>
     <row r="167">
@@ -2272,7 +2272,7 @@
         <v>2849377</v>
       </c>
       <c r="C167" t="n">
-        <v>44283</v>
+        <v>44282</v>
       </c>
     </row>
     <row r="168">
@@ -2283,7 +2283,7 @@
         <v>2482257</v>
       </c>
       <c r="C168" t="n">
-        <v>37981</v>
+        <v>37976</v>
       </c>
     </row>
     <row r="169">
@@ -2294,7 +2294,7 @@
         <v>2638190</v>
       </c>
       <c r="C169" t="n">
-        <v>40496</v>
+        <v>40494</v>
       </c>
     </row>
     <row r="170">
@@ -2305,7 +2305,7 @@
         <v>2988204</v>
       </c>
       <c r="C170" t="n">
-        <v>43843</v>
+        <v>43835</v>
       </c>
     </row>
     <row r="171">
@@ -2316,7 +2316,7 @@
         <v>2881272</v>
       </c>
       <c r="C171" t="n">
-        <v>47528</v>
+        <v>47521</v>
       </c>
     </row>
     <row r="172">
@@ -2327,7 +2327,7 @@
         <v>2563971</v>
       </c>
       <c r="C172" t="n">
-        <v>41243</v>
+        <v>41239</v>
       </c>
     </row>
     <row r="173">
@@ -2338,7 +2338,7 @@
         <v>2981485</v>
       </c>
       <c r="C173" t="n">
-        <v>45908</v>
+        <v>45907</v>
       </c>
     </row>
     <row r="174">
@@ -2349,7 +2349,7 @@
         <v>2876770</v>
       </c>
       <c r="C174" t="n">
-        <v>45910</v>
+        <v>45907</v>
       </c>
     </row>
     <row r="175">
@@ -2360,7 +2360,7 @@
         <v>2571215</v>
       </c>
       <c r="C175" t="n">
-        <v>39479</v>
+        <v>39477</v>
       </c>
     </row>
     <row r="176">
@@ -2371,7 +2371,7 @@
         <v>2656150</v>
       </c>
       <c r="C176" t="n">
-        <v>39903</v>
+        <v>39902</v>
       </c>
     </row>
     <row r="177">
@@ -2382,7 +2382,7 @@
         <v>2910453</v>
       </c>
       <c r="C177" t="n">
-        <v>43741</v>
+        <v>43740</v>
       </c>
     </row>
     <row r="178">
@@ -2393,7 +2393,7 @@
         <v>2904610</v>
       </c>
       <c r="C178" t="n">
-        <v>45763</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="179">
@@ -2404,7 +2404,7 @@
         <v>2575625</v>
       </c>
       <c r="C179" t="n">
-        <v>40858</v>
+        <v>40857</v>
       </c>
     </row>
     <row r="180">
@@ -2415,7 +2415,7 @@
         <v>2930672</v>
       </c>
       <c r="C180" t="n">
-        <v>46027</v>
+        <v>46026</v>
       </c>
     </row>
     <row r="181">
@@ -2426,7 +2426,7 @@
         <v>2690919</v>
       </c>
       <c r="C181" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="182">
@@ -2437,7 +2437,7 @@
         <v>2477905</v>
       </c>
       <c r="C182" t="n">
-        <v>43102</v>
+        <v>43095</v>
       </c>
     </row>
     <row r="183">
@@ -2448,7 +2448,7 @@
         <v>2654017</v>
       </c>
       <c r="C183" t="n">
-        <v>43583</v>
+        <v>43578</v>
       </c>
     </row>
     <row r="184">
@@ -2459,7 +2459,7 @@
         <v>2901753</v>
       </c>
       <c r="C184" t="n">
-        <v>48729</v>
+        <v>48724</v>
       </c>
     </row>
     <row r="185">
@@ -2470,7 +2470,7 @@
         <v>2572397</v>
       </c>
       <c r="C185" t="n">
-        <v>50709</v>
+        <v>50687</v>
       </c>
     </row>
     <row r="186">
